--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,317 +497,364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="20.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="14.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="12.7109375" customWidth="1" style="5" min="5" max="8"/>
+    <col width="23.7109375" customWidth="1" style="5" min="9" max="9"/>
+    <col width="25.7109375" customWidth="1" style="5" min="10" max="10"/>
+    <col width="19.7109375" customWidth="1" style="5" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>EnemyStat</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>@scope</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ce44b75f1366ea03</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>7371b7efcb839c1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>difficulty_key</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>hp_decimal</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>atk_decimal</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>def_decimal</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>spd_decimal</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>effect_hit_rate_decimal</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>effect_resistance_decimal</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>crit_damage_decimal</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>difficulty_key</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>hp_decimal</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>atk_decimal</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>def_decimal</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>spd_decimal</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>effect_hit_rate_decimal</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>effect_resistance_decimal</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>crit_damage_decimal</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;EnemyVariant.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>#scope</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>range=1..100</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>length=1..80</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -758,10 +890,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -801,10 +938,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -844,10 +986,15 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -892,6 +1039,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
@@ -935,6 +1087,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
@@ -973,10 +1130,15 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1016,10 +1178,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1059,10 +1226,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1102,10 +1274,15 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1145,10 +1322,15 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1188,10 +1370,15 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1231,10 +1418,15 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1274,10 +1466,15 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1317,10 +1514,15 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1360,10 +1562,15 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -1408,6 +1615,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
@@ -1446,16 +1658,219 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>56</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>56487</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.324</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>72</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>88816</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>90</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>514058</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>81</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>267655</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1864,6 +1864,54 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1912,6 +1912,54 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>27</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1960,6 +1960,390 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>44</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>13551</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>50</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20590</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>66</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>75</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>112994</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>84</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>167044</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2344,6 +2344,198 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>56</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>75316</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.324</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>72</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>118422</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>90</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>685410</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>81</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>356874</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2536,6 +2536,198 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>55</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>27850</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>72</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>78560</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>81</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>115683</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C46" t="n">
+        <v>90</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>175982</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2728,6 +2728,294 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>35</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4463</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>50</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>13384</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>67</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>49755</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.136</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.268</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>72</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>63830</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.288</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>81</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>93992</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>90</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>142985</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -3016,6 +3016,342 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>44</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>13551</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>49</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19417</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>50</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20590</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C57" t="n">
+        <v>66</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>75</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>112994</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>84</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>167044</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -3352,6 +3352,198 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>56</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>41422</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.324</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>72</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>108021</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>81</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>159064</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>90</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>241975</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -3544,6 +3544,198 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>50</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>18531</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>72</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>88380</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>130.9</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.288</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>81</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>130143</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C67" t="n">
+        <v>90</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>197980</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>157.08</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -3736,6 +3736,246 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>42</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>8403</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>67</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>57410</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.136</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>72</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>73650</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>81</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>108452</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>90</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>164983</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1482,7 +1482,7 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1530,7 +1530,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1578,44 +1578,44 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>56487</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1626,44 +1626,44 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>99</v>
+        <v>980001</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1677,7 +1677,7 @@
         <v>980001</v>
       </c>
       <c r="C25" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1686,32 +1686,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>56487</t>
+          <t>514058</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>980001</v>
       </c>
       <c r="C26" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1734,32 +1734,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>88816</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1782,32 +1782,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>514058</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1818,10 +1818,10 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C28" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1830,32 +1830,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>267655</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1926,22 +1926,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1965,7 +1965,7 @@
         <v>1010001</v>
       </c>
       <c r="C31" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1974,17 +1974,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2013,7 +2013,7 @@
         <v>1010001</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2061,7 +2061,7 @@
         <v>1010001</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2109,7 +2109,7 @@
         <v>1010001</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2157,7 +2157,7 @@
         <v>1010001</v>
       </c>
       <c r="C35" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2205,7 +2205,7 @@
         <v>1010001</v>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C37" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2262,32 +2262,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>75316</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2298,10 +2298,10 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C38" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2310,32 +2310,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>118422</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2349,7 +2349,7 @@
         <v>1020001</v>
       </c>
       <c r="C39" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2358,32 +2358,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>685410</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2397,7 +2397,7 @@
         <v>1020001</v>
       </c>
       <c r="C40" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2406,32 +2406,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>356874</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2442,10 +2442,10 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C41" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>685410</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>0.32</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0.4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2490,10 +2490,10 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C42" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2502,32 +2502,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>356874</t>
+          <t>78560</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2541,7 +2541,7 @@
         <v>1030001</v>
       </c>
       <c r="C43" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>115683</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2589,7 +2589,7 @@
         <v>1030001</v>
       </c>
       <c r="C44" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>175982</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2634,10 +2634,10 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C45" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2646,32 +2646,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>115683</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C46" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2694,32 +2694,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>175982</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2733,7 +2733,7 @@
         <v>1040001</v>
       </c>
       <c r="C47" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2742,32 +2742,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>339</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2781,7 +2781,7 @@
         <v>1040001</v>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>63830</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>383</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2829,7 +2829,7 @@
         <v>1040001</v>
       </c>
       <c r="C49" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2838,32 +2838,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>469</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2877,7 +2877,7 @@
         <v>1040001</v>
       </c>
       <c r="C50" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2886,32 +2886,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>142985</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>552</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C51" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2934,32 +2934,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>93992</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2970,10 +2970,10 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C52" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2982,32 +2982,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>142985</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3021,7 +3021,7 @@
         <v>1050001</v>
       </c>
       <c r="C53" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3030,17 +3030,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3069,7 +3069,7 @@
         <v>1050001</v>
       </c>
       <c r="C54" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3078,17 +3078,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3117,7 +3117,7 @@
         <v>1050001</v>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3126,32 +3126,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3165,7 +3165,7 @@
         <v>1050001</v>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3174,32 +3174,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3213,7 +3213,7 @@
         <v>1050001</v>
       </c>
       <c r="C57" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3222,32 +3222,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3258,10 +3258,10 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C58" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3270,32 +3270,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>41422</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>297</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3306,10 +3306,10 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C59" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3318,32 +3318,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>108021</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3357,7 +3357,7 @@
         <v>1060001</v>
       </c>
       <c r="C60" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3366,32 +3366,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>41422</t>
+          <t>159064</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3405,7 +3405,7 @@
         <v>1060001</v>
       </c>
       <c r="C61" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3414,32 +3414,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>108021</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C62" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3462,32 +3462,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>159064</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C63" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>130.9</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3549,7 +3549,7 @@
         <v>1070001</v>
       </c>
       <c r="C64" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>130143</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3597,7 +3597,7 @@
         <v>1070001</v>
       </c>
       <c r="C65" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>88380</t>
+          <t>197980</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>130.9</t>
+          <t>157.08</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3642,10 +3642,10 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C66" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3654,27 +3654,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C67" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3702,32 +3702,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>197980</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>407</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>157.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3741,7 +3741,7 @@
         <v>1080001</v>
       </c>
       <c r="C68" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3750,32 +3750,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3789,7 +3789,7 @@
         <v>1080001</v>
       </c>
       <c r="C69" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3798,32 +3798,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>57410</t>
+          <t>108452</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3837,7 +3837,7 @@
         <v>1080001</v>
       </c>
       <c r="C70" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3846,32 +3846,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>73650</t>
+          <t>164983</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3882,10 +3882,10 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C71" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3894,32 +3894,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>108452</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C72" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3942,35 +3942,2771 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>164983</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C73" t="n">
+        <v>32</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C74" t="n">
+        <v>34</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C75" t="n">
+        <v>36</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>9445</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C76" t="n">
+        <v>37</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C77" t="n">
+        <v>44</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C78" t="n">
+        <v>44</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>14906</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>95</v>
+      </c>
+      <c r="C79" t="n">
+        <v>47</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C80" t="n">
+        <v>47</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3414</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C81" t="n">
+        <v>47</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>30728</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>96</v>
+      </c>
+      <c r="C82" t="n">
+        <v>49</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19417</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>96</v>
+      </c>
+      <c r="C84" t="n">
+        <v>50</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>20590</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C85" t="n">
+        <v>50</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>24708</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C86" t="n">
+        <v>50</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>24708</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C87" t="n">
+        <v>51</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C88" t="n">
+        <v>51</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>95</v>
+      </c>
+      <c r="C89" t="n">
+        <v>51</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C90" t="n">
+        <v>51</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>4687</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>95</v>
+      </c>
+      <c r="C91" t="n">
+        <v>52</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.108</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C92" t="n">
+        <v>52</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.108</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C93" t="n">
+        <v>53</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>43685</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C94" t="n">
+        <v>53</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>52421</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C95" t="n">
+        <v>54</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C96" t="n">
+        <v>54</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>4476</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" t="n">
+        <v>54</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C98" t="n">
+        <v>54</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>6394</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C99" t="n">
+        <v>57</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>95</v>
+      </c>
+      <c r="C100" t="n">
+        <v>57</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>6480</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C101" t="n">
+        <v>57</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C102" t="n">
+        <v>61</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>58260</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.244</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C103" t="n">
+        <v>61</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>68853</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.244</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>96</v>
+      </c>
+      <c r="C104" t="n">
+        <v>66</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C105" t="n">
+        <v>66</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>79878</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C106" t="n">
+        <v>66</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>87139</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C107" t="n">
+        <v>66</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>87139</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C108" t="n">
+        <v>66</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>94401</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C109" t="n">
+        <v>69</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>126612</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C110" t="n">
+        <v>69</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>151934</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>189.2</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>96</v>
+      </c>
+      <c r="C111" t="n">
+        <v>75</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>112994</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C112" t="n">
+        <v>75</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>124293</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C113" t="n">
+        <v>75</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>135593</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C114" t="n">
+        <v>75</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>135593</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C115" t="n">
+        <v>75</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>146892</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C116" t="n">
+        <v>78</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>191682</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C117" t="n">
+        <v>78</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>230018</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>206.4</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C118" t="n">
+        <v>21</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>96</v>
+      </c>
+      <c r="C119" t="n">
+        <v>84</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>167044</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C120" t="n">
+        <v>84</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>183748</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C121" t="n">
+        <v>84</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>200453</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C122" t="n">
+        <v>84</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>200453</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C123" t="n">
+        <v>84</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>217157</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C124" t="n">
+        <v>22</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C125" t="n">
+        <v>87</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>288105</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C126" t="n">
+        <v>87</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>345726</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>227.04</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C127" t="n">
+        <v>24</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C128" t="n">
+        <v>25</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C129" t="n">
+        <v>29</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -858,7 +858,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -906,7 +906,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -918,7 +918,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -954,10 +954,10 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1002,7 +1002,7 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="n">
         <v>16</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19.565216</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19.565216</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1146,7 +1146,7 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1194,7 +1194,7 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1242,7 +1242,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1290,7 +1290,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1338,7 +1338,7 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1386,7 +1386,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1434,44 +1434,44 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>56487</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1482,44 +1482,44 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1530,44 +1530,44 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>99</v>
+        <v>980001</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>514058</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>980001</v>
       </c>
       <c r="C23" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>56487</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C24" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1638,32 +1638,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>88816</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C25" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1686,32 +1686,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>514058</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1722,10 +1722,10 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C26" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1734,32 +1734,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>267655</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1782,22 +1782,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1818,10 +1818,10 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1830,22 +1830,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1869,7 +1869,7 @@
         <v>1010001</v>
       </c>
       <c r="C29" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1878,17 +1878,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1917,7 +1917,7 @@
         <v>1010001</v>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1926,32 +1926,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1965,7 +1965,7 @@
         <v>1010001</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1974,17 +1974,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2013,7 +2013,7 @@
         <v>1010001</v>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2061,7 +2061,7 @@
         <v>1010001</v>
       </c>
       <c r="C33" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2106,10 +2106,10 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2118,32 +2118,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>75316</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2154,10 +2154,10 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C35" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2166,32 +2166,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>118422</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C36" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>685410</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2253,7 +2253,7 @@
         <v>1020001</v>
       </c>
       <c r="C37" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2262,32 +2262,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>356874</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2298,10 +2298,10 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C38" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2310,32 +2310,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C39" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2358,32 +2358,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>685410</t>
+          <t>78560</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2394,7 +2394,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C40" t="n">
         <v>81</v>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>356874</t>
+          <t>115683</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>1030001</v>
       </c>
       <c r="C41" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>175982</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2490,10 +2490,10 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C42" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2502,32 +2502,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C43" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>115683</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C44" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>175982</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>339</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2637,7 +2637,7 @@
         <v>1040001</v>
       </c>
       <c r="C45" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2646,32 +2646,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>63830</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>383</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2685,7 +2685,7 @@
         <v>1040001</v>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2694,32 +2694,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>469</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2733,7 +2733,7 @@
         <v>1040001</v>
       </c>
       <c r="C47" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2742,32 +2742,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>142985</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>552</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2778,10 +2778,10 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C48" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2826,10 +2826,10 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C49" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2838,32 +2838,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>93992</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C50" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2886,32 +2886,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>142985</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2925,7 +2925,7 @@
         <v>1050001</v>
       </c>
       <c r="C51" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2973,7 +2973,7 @@
         <v>1050001</v>
       </c>
       <c r="C52" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2982,32 +2982,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3021,7 +3021,7 @@
         <v>1050001</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3030,32 +3030,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3069,7 +3069,7 @@
         <v>1050001</v>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3078,32 +3078,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3114,10 +3114,10 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C55" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3126,32 +3126,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>41422</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>297</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3162,10 +3162,10 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C56" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3174,32 +3174,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>108021</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3210,10 +3210,10 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C57" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3222,32 +3222,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>159064</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3261,7 +3261,7 @@
         <v>1060001</v>
       </c>
       <c r="C58" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3270,32 +3270,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>41422</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3306,10 +3306,10 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C59" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3318,32 +3318,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>108021</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C60" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3366,32 +3366,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>159064</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>130.9</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C61" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3414,32 +3414,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>130143</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3453,7 +3453,7 @@
         <v>1070001</v>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3462,32 +3462,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>197980</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>157.08</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C63" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>88380</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>130.9</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3546,10 +3546,10 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C64" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>407</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C65" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>197980</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>157.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3645,7 +3645,7 @@
         <v>1080001</v>
       </c>
       <c r="C66" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3654,32 +3654,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>108452</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3693,7 +3693,7 @@
         <v>1080001</v>
       </c>
       <c r="C67" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3702,32 +3702,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>57410</t>
+          <t>164983</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3738,10 +3738,10 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C68" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3750,32 +3750,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>73650</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3786,10 +3786,10 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C69" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3798,32 +3798,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>108452</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C70" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3846,32 +3846,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>164983</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>520</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3885,7 +3885,7 @@
         <v>1090009</v>
       </c>
       <c r="C71" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3894,17 +3894,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1090012</v>
+        <v>1090011</v>
       </c>
       <c r="C72" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3942,22 +3942,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3978,10 +3978,10 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1090012</v>
+        <v>1090009</v>
       </c>
       <c r="C73" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3990,17 +3990,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C74" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1090011</v>
+        <v>1090010</v>
       </c>
       <c r="C75" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4086,22 +4086,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4122,10 +4122,10 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1090009</v>
+        <v>95</v>
       </c>
       <c r="C76" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4134,22 +4134,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1090012</v>
+        <v>1090004</v>
       </c>
       <c r="C77" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4182,17 +4182,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4218,10 +4218,10 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090010</v>
+        <v>1090002</v>
       </c>
       <c r="C78" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4230,22 +4230,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4266,10 +4266,10 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C79" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4278,22 +4278,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4314,10 +4314,10 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1090004</v>
+        <v>1090005</v>
       </c>
       <c r="C80" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4326,22 +4326,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4362,10 +4362,10 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1090002</v>
+        <v>96</v>
       </c>
       <c r="C81" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4410,10 +4410,10 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C82" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4422,22 +4422,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090005</v>
+        <v>1090003</v>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4470,22 +4470,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4506,10 +4506,10 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>96</v>
+        <v>1090005</v>
       </c>
       <c r="C84" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -4518,32 +4518,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090008</v>
+        <v>1090012</v>
       </c>
       <c r="C85" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4566,32 +4566,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090003</v>
+        <v>95</v>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4614,32 +4614,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4650,7 +4650,7 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C87" t="n">
         <v>51</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4698,10 +4698,10 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1090012</v>
+        <v>95</v>
       </c>
       <c r="C88" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4710,32 +4710,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C89" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4758,32 +4758,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4794,10 +4794,10 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C90" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4806,32 +4806,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>43685</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4842,10 +4842,10 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C91" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4854,32 +4854,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4890,10 +4890,10 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090004</v>
+        <v>1090005</v>
       </c>
       <c r="C92" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -4902,32 +4902,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>0.016</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.108</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4938,10 +4938,10 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C93" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1090002</v>
+        <v>95</v>
       </c>
       <c r="C94" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4998,32 +4998,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5034,7 +5034,7 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C95" t="n">
         <v>54</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5082,10 +5082,10 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C96" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5094,17 +5094,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -5142,17 +5142,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>1090004</v>
       </c>
       <c r="C98" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1090012</v>
+        <v>1090010</v>
       </c>
       <c r="C99" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -5238,32 +5238,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>58260</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.244</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5274,10 +5274,10 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C100" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -5286,32 +5286,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>68853</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.244</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5322,10 +5322,10 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C101" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5334,32 +5334,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5373,7 +5373,7 @@
         <v>1090010</v>
       </c>
       <c r="C102" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -5382,32 +5382,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>58260</t>
+          <t>79878</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090011</v>
+        <v>1090008</v>
       </c>
       <c r="C103" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5430,32 +5430,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5466,7 +5466,7 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C104" t="n">
         <v>66</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5514,7 +5514,7 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C105" t="n">
         <v>66</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>79878</t>
+          <t>94401</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C106" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -5574,17 +5574,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>126612</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5610,10 +5610,10 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1090003</v>
+        <v>1090002</v>
       </c>
       <c r="C107" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5622,32 +5622,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>151934</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>189.2</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5658,10 +5658,10 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1090011</v>
+        <v>96</v>
       </c>
       <c r="C108" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -5670,32 +5670,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>94401</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1090006</v>
+        <v>1090010</v>
       </c>
       <c r="C109" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -5718,32 +5718,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>124293</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5754,10 +5754,10 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1090002</v>
+        <v>1090008</v>
       </c>
       <c r="C110" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -5766,32 +5766,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>151934</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>189.2</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5802,7 +5802,7 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C111" t="n">
         <v>75</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5850,7 +5850,7 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C112" t="n">
         <v>75</v>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>146892</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5898,10 +5898,10 @@
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C113" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -5910,27 +5910,27 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>191682</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>529</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1090003</v>
+        <v>1090002</v>
       </c>
       <c r="C114" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -5958,27 +5958,27 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>230018</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>529</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>206.4</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5994,10 +5994,10 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1090011</v>
+        <v>1090005</v>
       </c>
       <c r="C115" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -6006,32 +6006,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>146892</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6042,10 +6042,10 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C116" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -6054,27 +6054,27 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>191682</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6090,10 +6090,10 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C117" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -6102,27 +6102,27 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>230018</t>
+          <t>183748</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>206.4</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6138,10 +6138,10 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C118" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -6150,32 +6150,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -6186,7 +6186,7 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C119" t="n">
         <v>84</v>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6234,7 +6234,7 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C120" t="n">
         <v>84</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>183748</t>
+          <t>217157</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6282,10 +6282,10 @@
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1090008</v>
+        <v>1090005</v>
       </c>
       <c r="C121" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>200453</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -6330,10 +6330,10 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C122" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -6342,27 +6342,27 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>200453</t>
+          <t>288105</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>630</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1090011</v>
+        <v>1090002</v>
       </c>
       <c r="C123" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -6390,27 +6390,27 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>217157</t>
+          <t>345726</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>630</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>227.04</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6429,7 +6429,7 @@
         <v>1090005</v>
       </c>
       <c r="C124" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -6438,17 +6438,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>440</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6474,10 +6474,10 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1090006</v>
+        <v>1090005</v>
       </c>
       <c r="C125" t="n">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6486,32 +6486,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>288105</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -6522,10 +6522,10 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C126" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -6534,32 +6534,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>345726</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>227.04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6570,10 +6570,10 @@
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1090005</v>
+        <v>97</v>
       </c>
       <c r="C127" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6582,17 +6582,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>396</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1090005</v>
+        <v>97</v>
       </c>
       <c r="C128" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -6630,17 +6630,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>520</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6666,10 +6666,10 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C129" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -6678,35 +6678,2195 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>485</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>36</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>7265</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>97</v>
+      </c>
+      <c r="C131" t="n">
+        <v>37</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>100</v>
+      </c>
+      <c r="C132" t="n">
+        <v>44</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>16261</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C133" t="n">
+        <v>44</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>24392</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C134" t="n">
+        <v>47</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>46092</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C135" t="n">
+        <v>49</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>19417</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C136" t="n">
+        <v>7</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C137" t="n">
+        <v>50</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>20590</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C138" t="n">
+        <v>50</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>37062</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C139" t="n">
+        <v>51</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C140" t="n">
+        <v>51</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>97</v>
+      </c>
+      <c r="C141" t="n">
+        <v>51</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C142" t="n">
+        <v>51</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C143" t="n">
+        <v>51</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>5273</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C144" t="n">
+        <v>52</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.108</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C145" t="n">
+        <v>53</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>49509</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C146" t="n">
+        <v>54</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>97</v>
+      </c>
+      <c r="C147" t="n">
+        <v>54</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2398</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C148" t="n">
+        <v>54</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C149" t="n">
+        <v>54</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>99</v>
+      </c>
+      <c r="C150" t="n">
+        <v>54</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C151" t="n">
+        <v>54</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>7193</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>99</v>
+      </c>
+      <c r="C152" t="n">
+        <v>55</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>7659</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C153" t="n">
+        <v>55</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C154" t="n">
+        <v>57</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C155" t="n">
+        <v>57</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>99</v>
+      </c>
+      <c r="C156" t="n">
+        <v>57</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>8910</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C157" t="n">
+        <v>57</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C158" t="n">
+        <v>61</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>52964</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>0.244</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C159" t="n">
+        <v>66</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>130709</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C160" t="n">
+        <v>66</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>189.2</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>100</v>
+      </c>
+      <c r="C161" t="n">
+        <v>66</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>87139</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C162" t="n">
+        <v>69</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>143494</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C163" t="n">
+        <v>75</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>112994</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>189.2</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>100</v>
+      </c>
+      <c r="C164" t="n">
+        <v>75</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>135593</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C165" t="n">
+        <v>75</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>203389</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C166" t="n">
+        <v>78</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>217240</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C167" t="n">
+        <v>21</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C168" t="n">
+        <v>84</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>167044</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>206.4</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>100</v>
+      </c>
+      <c r="C169" t="n">
+        <v>84</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>200453</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C170" t="n">
+        <v>84</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>300679</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C171" t="n">
+        <v>22</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C172" t="n">
+        <v>87</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>326519</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C173" t="n">
+        <v>24</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C174" t="n">
+        <v>25</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -918,12 +918,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19.565216</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -954,10 +954,10 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1002,10 +1002,10 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.565216</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1146,7 +1146,7 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1194,7 +1194,7 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1242,7 +1242,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1290,44 +1290,44 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>56487</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1338,44 +1338,44 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1386,44 +1386,44 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>standard-v1</t>
+          <t>standard-universe-v1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>514058</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1437,7 +1437,7 @@
         <v>980001</v>
       </c>
       <c r="C20" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>56487</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1494,32 +1494,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>88816</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1542,32 +1542,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>514058</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C23" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>267655</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1686,22 +1686,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>1010001</v>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1734,17 +1734,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1773,7 +1773,7 @@
         <v>1010001</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1782,32 +1782,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1821,7 +1821,7 @@
         <v>1010001</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1830,17 +1830,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1869,7 +1869,7 @@
         <v>1010001</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1917,7 +1917,7 @@
         <v>1010001</v>
       </c>
       <c r="C30" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1926,32 +1926,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1974,32 +1974,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>75316</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2010,10 +2010,10 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C32" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>118422</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C33" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>685410</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>876</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2109,7 +2109,7 @@
         <v>1020001</v>
       </c>
       <c r="C34" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2118,32 +2118,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>356874</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>881</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2154,10 +2154,10 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C35" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2166,32 +2166,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>685410</t>
+          <t>78560</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2250,7 +2250,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C37" t="n">
         <v>81</v>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>356874</t>
+          <t>115683</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2301,7 +2301,7 @@
         <v>1030001</v>
       </c>
       <c r="C38" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2310,32 +2310,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>175982</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C39" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2358,32 +2358,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C40" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2406,32 +2406,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>115683</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2442,10 +2442,10 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C41" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>175982</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>339</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2493,7 +2493,7 @@
         <v>1040001</v>
       </c>
       <c r="C42" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2502,32 +2502,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>63830</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>383</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2541,7 +2541,7 @@
         <v>1040001</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>469</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2589,7 +2589,7 @@
         <v>1040001</v>
       </c>
       <c r="C44" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>142985</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>552</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2634,10 +2634,10 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C45" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2646,32 +2646,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C46" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2694,32 +2694,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>93992</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C47" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2742,32 +2742,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>142985</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2781,7 +2781,7 @@
         <v>1050001</v>
       </c>
       <c r="C48" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2829,7 +2829,7 @@
         <v>1050001</v>
       </c>
       <c r="C49" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2838,32 +2838,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2877,7 +2877,7 @@
         <v>1050001</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2886,32 +2886,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2925,7 +2925,7 @@
         <v>1050001</v>
       </c>
       <c r="C51" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2934,32 +2934,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2970,10 +2970,10 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C52" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2982,32 +2982,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>41422</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>297</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3018,10 +3018,10 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C53" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3030,32 +3030,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>108021</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3066,10 +3066,10 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C54" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3078,32 +3078,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>159064</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3117,7 +3117,7 @@
         <v>1060001</v>
       </c>
       <c r="C55" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3126,32 +3126,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41422</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3162,10 +3162,10 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C56" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3174,32 +3174,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>108021</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3210,10 +3210,10 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C57" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3222,32 +3222,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>159064</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>130.9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3258,10 +3258,10 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C58" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3270,32 +3270,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>130143</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3309,7 +3309,7 @@
         <v>1070001</v>
       </c>
       <c r="C59" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3318,32 +3318,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>197980</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>157.08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C60" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3366,32 +3366,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>88380</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>130.9</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C61" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3414,32 +3414,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>407</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C62" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3462,32 +3462,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>197980</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>459</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>920</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>157.08</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3501,7 +3501,7 @@
         <v>1080001</v>
       </c>
       <c r="C63" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3510,32 +3510,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>108452</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>563</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3549,7 +3549,7 @@
         <v>1080001</v>
       </c>
       <c r="C64" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>57410</t>
+          <t>164983</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C65" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>73650</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3642,10 +3642,10 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C66" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3654,32 +3654,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>108452</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C67" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3702,32 +3702,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>164983</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>520</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3741,7 +3741,7 @@
         <v>1090009</v>
       </c>
       <c r="C68" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3750,17 +3750,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3786,10 +3786,10 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1090012</v>
+        <v>1090011</v>
       </c>
       <c r="C69" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3798,22 +3798,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1090012</v>
+        <v>1090009</v>
       </c>
       <c r="C70" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3882,10 +3882,10 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C71" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3894,17 +3894,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1090011</v>
+        <v>1090010</v>
       </c>
       <c r="C72" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3942,22 +3942,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3978,10 +3978,10 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1090009</v>
+        <v>95</v>
       </c>
       <c r="C73" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3990,22 +3990,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1090012</v>
+        <v>1090004</v>
       </c>
       <c r="C74" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1090010</v>
+        <v>1090002</v>
       </c>
       <c r="C75" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4086,22 +4086,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4122,10 +4122,10 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C76" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4134,22 +4134,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1090004</v>
+        <v>1090005</v>
       </c>
       <c r="C77" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4182,22 +4182,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4218,10 +4218,10 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090002</v>
+        <v>96</v>
       </c>
       <c r="C78" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4230,22 +4230,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4266,10 +4266,10 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C79" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4278,22 +4278,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4314,10 +4314,10 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1090005</v>
+        <v>1090003</v>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4326,22 +4326,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4362,10 +4362,10 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>96</v>
+        <v>1090005</v>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4374,32 +4374,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4410,10 +4410,10 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1090008</v>
+        <v>1090012</v>
       </c>
       <c r="C82" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4422,32 +4422,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090003</v>
+        <v>95</v>
       </c>
       <c r="C83" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4506,7 +4506,7 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C84" t="n">
         <v>51</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090012</v>
+        <v>95</v>
       </c>
       <c r="C85" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4566,32 +4566,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C86" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4614,32 +4614,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4650,10 +4650,10 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C87" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -4662,32 +4662,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>43685</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4698,10 +4698,10 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>95</v>
+        <v>1090002</v>
       </c>
       <c r="C88" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4710,32 +4710,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1090004</v>
+        <v>1090005</v>
       </c>
       <c r="C89" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4758,32 +4758,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>0.016</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>0.108</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4794,10 +4794,10 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1090006</v>
+        <v>1090009</v>
       </c>
       <c r="C90" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4806,32 +4806,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4842,10 +4842,10 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1090002</v>
+        <v>95</v>
       </c>
       <c r="C91" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4854,32 +4854,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C92" t="n">
         <v>54</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4938,10 +4938,10 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C93" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4950,17 +4950,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4989,7 +4989,7 @@
         <v>95</v>
       </c>
       <c r="C94" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5037,7 +5037,7 @@
         <v>1090004</v>
       </c>
       <c r="C95" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5046,17 +5046,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5082,10 +5082,10 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090012</v>
+        <v>1090010</v>
       </c>
       <c r="C96" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5094,32 +5094,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>58260</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.244</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C97" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -5142,32 +5142,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>68853</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.244</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C98" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5229,7 +5229,7 @@
         <v>1090010</v>
       </c>
       <c r="C99" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -5238,32 +5238,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>58260</t>
+          <t>79878</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5274,10 +5274,10 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1090011</v>
+        <v>1090008</v>
       </c>
       <c r="C100" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -5286,32 +5286,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5322,7 +5322,7 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C101" t="n">
         <v>66</v>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5370,7 +5370,7 @@
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C102" t="n">
         <v>66</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>79878</t>
+          <t>94401</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C103" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5430,17 +5430,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>126612</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5466,10 +5466,10 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1090003</v>
+        <v>1090002</v>
       </c>
       <c r="C104" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -5478,32 +5478,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>151934</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>189.2</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5514,10 +5514,10 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1090011</v>
+        <v>96</v>
       </c>
       <c r="C105" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -5526,32 +5526,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>94401</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1090006</v>
+        <v>1090010</v>
       </c>
       <c r="C106" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -5574,32 +5574,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>124293</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5610,10 +5610,10 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1090002</v>
+        <v>1090008</v>
       </c>
       <c r="C107" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5622,32 +5622,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>151934</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>189.2</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5658,7 +5658,7 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C108" t="n">
         <v>75</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5706,7 +5706,7 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C109" t="n">
         <v>75</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>146892</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5754,10 +5754,10 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1090008</v>
+        <v>1090006</v>
       </c>
       <c r="C110" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -5766,27 +5766,27 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>191682</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>529</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5802,10 +5802,10 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1090003</v>
+        <v>1090002</v>
       </c>
       <c r="C111" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -5814,27 +5814,27 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>230018</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>529</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>206.4</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5850,10 +5850,10 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1090011</v>
+        <v>1090005</v>
       </c>
       <c r="C112" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -5862,32 +5862,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>146892</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -5898,10 +5898,10 @@
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C113" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -5910,27 +5910,27 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>191682</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C114" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -5958,27 +5958,27 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>230018</t>
+          <t>183748</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>206.4</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5994,10 +5994,10 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C115" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -6006,32 +6006,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6042,7 +6042,7 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C116" t="n">
         <v>84</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6090,7 +6090,7 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C117" t="n">
         <v>84</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>183748</t>
+          <t>217157</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6138,10 +6138,10 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090008</v>
+        <v>1090005</v>
       </c>
       <c r="C118" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -6150,32 +6150,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>200453</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -6186,10 +6186,10 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C119" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -6198,27 +6198,27 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>200453</t>
+          <t>288105</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>630</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1090011</v>
+        <v>1090002</v>
       </c>
       <c r="C120" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -6246,27 +6246,27 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>217157</t>
+          <t>345726</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>630</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>227.04</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6285,7 +6285,7 @@
         <v>1090005</v>
       </c>
       <c r="C121" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -6294,17 +6294,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>440</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6330,10 +6330,10 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1090006</v>
+        <v>1090005</v>
       </c>
       <c r="C122" t="n">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -6342,32 +6342,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>288105</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6378,10 +6378,10 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C123" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -6390,32 +6390,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>345726</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>227.04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6426,10 +6426,10 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1090005</v>
+        <v>97</v>
       </c>
       <c r="C124" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -6438,17 +6438,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>396</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6474,10 +6474,10 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1090005</v>
+        <v>97</v>
       </c>
       <c r="C125" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6486,17 +6486,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>520</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -6522,10 +6522,10 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1090010</v>
+        <v>97</v>
       </c>
       <c r="C126" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -6534,22 +6534,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>485</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6570,10 +6570,10 @@
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C127" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6582,22 +6582,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6621,7 +6621,7 @@
         <v>97</v>
       </c>
       <c r="C128" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -6630,17 +6630,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6666,10 +6666,10 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C129" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -6678,22 +6678,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -6714,10 +6714,10 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C130" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -6726,22 +6726,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6762,10 +6762,10 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>97</v>
+        <v>1100009</v>
       </c>
       <c r="C131" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6774,22 +6774,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>46092</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -6810,10 +6810,10 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>100</v>
+        <v>1100004</v>
       </c>
       <c r="C132" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6822,22 +6822,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6858,10 +6858,10 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C133" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -6870,22 +6870,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -6906,10 +6906,10 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1100009</v>
+        <v>1100004</v>
       </c>
       <c r="C134" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6918,22 +6918,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6954,10 +6954,10 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C135" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6966,22 +6966,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7005,7 +7005,7 @@
         <v>1100002</v>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -7014,17 +7014,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7050,10 +7050,10 @@
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1100004</v>
+        <v>1100011</v>
       </c>
       <c r="C137" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -7062,32 +7062,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1100010</v>
+        <v>97</v>
       </c>
       <c r="C138" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -7110,32 +7110,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -7146,7 +7146,7 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1100002</v>
+        <v>1100003</v>
       </c>
       <c r="C139" t="n">
         <v>51</v>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -7194,7 +7194,7 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1100011</v>
+        <v>1100012</v>
       </c>
       <c r="C140" t="n">
         <v>51</v>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -7242,10 +7242,10 @@
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C141" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -7254,32 +7254,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>720</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -7290,10 +7290,10 @@
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1100003</v>
+        <v>1100007</v>
       </c>
       <c r="C142" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -7302,32 +7302,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -7338,10 +7338,10 @@
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1100012</v>
+        <v>1100011</v>
       </c>
       <c r="C143" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -7350,32 +7350,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -7386,10 +7386,10 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1100003</v>
+        <v>97</v>
       </c>
       <c r="C144" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -7398,32 +7398,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -7434,10 +7434,10 @@
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="C145" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -7446,32 +7446,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -7482,7 +7482,7 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1100011</v>
+        <v>1100003</v>
       </c>
       <c r="C146" t="n">
         <v>54</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -7530,7 +7530,7 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C147" t="n">
         <v>54</v>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7578,7 +7578,7 @@
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1100006</v>
+        <v>1100012</v>
       </c>
       <c r="C148" t="n">
         <v>54</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7626,10 +7626,10 @@
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1100003</v>
+        <v>99</v>
       </c>
       <c r="C149" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -7638,32 +7638,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -7674,10 +7674,10 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>99</v>
+        <v>1100012</v>
       </c>
       <c r="C150" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -7686,32 +7686,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -7722,10 +7722,10 @@
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1100012</v>
+        <v>1100011</v>
       </c>
       <c r="C151" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -7734,32 +7734,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -7770,10 +7770,10 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>99</v>
+        <v>1100006</v>
       </c>
       <c r="C152" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -7782,32 +7782,32 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -7818,10 +7818,10 @@
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1100012</v>
+        <v>99</v>
       </c>
       <c r="C153" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -7830,32 +7830,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1100011</v>
+        <v>1100012</v>
       </c>
       <c r="C154" t="n">
         <v>57</v>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -7914,10 +7914,10 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1100006</v>
+        <v>1100004</v>
       </c>
       <c r="C155" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -7926,32 +7926,32 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>52964</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.244</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -7962,10 +7962,10 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>99</v>
+        <v>1100010</v>
       </c>
       <c r="C156" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -7974,32 +7974,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>130709</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -8010,10 +8010,10 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1100012</v>
+        <v>1100004</v>
       </c>
       <c r="C157" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -8022,32 +8022,32 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>189.2</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -8058,10 +8058,10 @@
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C158" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -8070,32 +8070,32 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>52964</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -8106,10 +8106,10 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="C159" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -8118,32 +8118,32 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>130709</t>
+          <t>143494</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>158.4</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -8157,7 +8157,7 @@
         <v>1100004</v>
       </c>
       <c r="C160" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -8166,17 +8166,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -8205,7 +8205,7 @@
         <v>100</v>
       </c>
       <c r="C161" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -8214,17 +8214,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -8250,10 +8250,10 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C162" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -8262,32 +8262,32 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>203389</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>158.4</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -8298,10 +8298,10 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1100004</v>
+        <v>1100007</v>
       </c>
       <c r="C163" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -8310,27 +8310,27 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>217240</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>529</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>189.2</t>
+          <t>172.8</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8346,10 +8346,10 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>100</v>
+        <v>1100002</v>
       </c>
       <c r="C164" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -8358,32 +8358,32 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -8394,10 +8394,10 @@
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1100010</v>
+        <v>1100004</v>
       </c>
       <c r="C165" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -8406,27 +8406,27 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>203389</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>206.4</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -8442,10 +8442,10 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C166" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -8454,27 +8454,27 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>217240</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>172.8</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8490,10 +8490,10 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1100002</v>
+        <v>1100010</v>
       </c>
       <c r="C167" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -8502,32 +8502,32 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>300679</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -8538,10 +8538,10 @@
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1100004</v>
+        <v>1100002</v>
       </c>
       <c r="C168" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -8550,32 +8550,32 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>206.4</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -8586,10 +8586,10 @@
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C169" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -8598,27 +8598,27 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>200453</t>
+          <t>326519</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>630</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>190.08</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -8634,10 +8634,10 @@
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C170" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -8646,32 +8646,32 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>300679</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>440</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -8685,7 +8685,7 @@
         <v>1100002</v>
       </c>
       <c r="C171" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -8694,17 +8694,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8730,10 +8730,10 @@
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1100007</v>
+        <v>103</v>
       </c>
       <c r="C172" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -8742,32 +8742,32 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>326519</t>
+          <t>316</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>190.08</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -8778,10 +8778,10 @@
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1100002</v>
+        <v>104</v>
       </c>
       <c r="C173" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -8790,17 +8790,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>316</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8826,10 +8826,10 @@
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1100002</v>
+        <v>103</v>
       </c>
       <c r="C174" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -8838,17 +8838,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>520</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8867,6 +8867,2022 @@
         </is>
       </c>
       <c r="K174" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>104</v>
+      </c>
+      <c r="C175" t="n">
+        <v>32</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>103</v>
+      </c>
+      <c r="C176" t="n">
+        <v>34</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>104</v>
+      </c>
+      <c r="C177" t="n">
+        <v>34</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C178" t="n">
+        <v>36</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>8718</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C179" t="n">
+        <v>44</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C180" t="n">
+        <v>44</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>3727</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>103</v>
+      </c>
+      <c r="C181" t="n">
+        <v>47</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C182" t="n">
+        <v>47</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2561</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C183" t="n">
+        <v>47</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C184" t="n">
+        <v>47</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>30728</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C185" t="n">
+        <v>47</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>35849</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C186" t="n">
+        <v>49</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>23300</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C187" t="n">
+        <v>50</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>37062</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>103</v>
+      </c>
+      <c r="C188" t="n">
+        <v>51</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>104</v>
+      </c>
+      <c r="C189" t="n">
+        <v>51</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C190" t="n">
+        <v>51</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C191" t="n">
+        <v>51</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C192" t="n">
+        <v>51</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C193" t="n">
+        <v>51</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>6445</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>103</v>
+      </c>
+      <c r="C194" t="n">
+        <v>52</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C195" t="n">
+        <v>52</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>7227</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>0.108</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>103</v>
+      </c>
+      <c r="C196" t="n">
+        <v>54</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>104</v>
+      </c>
+      <c r="C197" t="n">
+        <v>54</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C198" t="n">
+        <v>54</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C199" t="n">
+        <v>54</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C200" t="n">
+        <v>54</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>102</v>
+      </c>
+      <c r="C201" t="n">
+        <v>54</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C202" t="n">
+        <v>54</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>5594</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C203" t="n">
+        <v>54</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>8791</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C204" t="n">
+        <v>55</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C205" t="n">
+        <v>57</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C206" t="n">
+        <v>57</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C207" t="n">
+        <v>57</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>11138</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>102</v>
+      </c>
+      <c r="C208" t="n">
+        <v>57</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>6075</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C209" t="n">
+        <v>57</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C210" t="n">
+        <v>61</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>63557</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>0.244</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C211" t="n">
+        <v>66</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>130709</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C212" t="n">
+        <v>66</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>87139</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C213" t="n">
+        <v>75</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>135593</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C214" t="n">
+        <v>75</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>203389</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C215" t="n">
+        <v>84</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>200453</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C216" t="n">
+        <v>84</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>300679</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/config/data/EnemyStat.xlsx
+++ b/config/data/EnemyStat.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K252"/>
+  <dimension ref="A1:K301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -12616,6 +12616,2358 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C253" t="n">
+        <v>32</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C254" t="n">
+        <v>39</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>12690</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C255" t="n">
+        <v>44</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>14906</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C256" t="n">
+        <v>44</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>18971</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C257" t="n">
+        <v>47</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C258" t="n">
+        <v>47</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C259" t="n">
+        <v>47</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>32435</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C260" t="n">
+        <v>50</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>22649</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C261" t="n">
+        <v>50</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>22649</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C262" t="n">
+        <v>50</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>28826</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C263" t="n">
+        <v>50</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>32944</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C264" t="n">
+        <v>53</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C265" t="n">
+        <v>53</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>55334</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C266" t="n">
+        <v>54</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C267" t="n">
+        <v>54</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C268" t="n">
+        <v>55</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>3829</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C269" t="n">
+        <v>55</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>7311</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C270" t="n">
+        <v>57</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>4455</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C271" t="n">
+        <v>57</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>8505</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C272" t="n">
+        <v>61</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>58260</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>0.244</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C273" t="n">
+        <v>64</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>103608</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>0.256</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C274" t="n">
+        <v>64</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>97133</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>0.256</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C275" t="n">
+        <v>66</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>101662</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C276" t="n">
+        <v>66</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>116186</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C277" t="n">
+        <v>66</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>79878</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C278" t="n">
+        <v>66</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>79878</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C279" t="n">
+        <v>66</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>79878</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>0.128</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C280" t="n">
+        <v>69</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>126612</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C281" t="n">
+        <v>69</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>135053</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C282" t="n">
+        <v>69</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>160375</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C283" t="n">
+        <v>75</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>124293</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C284" t="n">
+        <v>75</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>124293</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C285" t="n">
+        <v>75</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>124293</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C286" t="n">
+        <v>75</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>158192</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C287" t="n">
+        <v>75</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>180790</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C288" t="n">
+        <v>78</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>191682</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C289" t="n">
+        <v>78</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>204461</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C290" t="n">
+        <v>78</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>242797</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>172.8</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C291" t="n">
+        <v>21</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>3322</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C292" t="n">
+        <v>84</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>183748</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C293" t="n">
+        <v>84</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>183748</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C294" t="n">
+        <v>84</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>183748</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C295" t="n">
+        <v>84</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>233862</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C296" t="n">
+        <v>84</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>267270</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>0.272</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C297" t="n">
+        <v>87</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>288105</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C298" t="n">
+        <v>87</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>307312</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>158.4</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C299" t="n">
+        <v>87</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>364933</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>190.08</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C300" t="n">
+        <v>24</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>5457</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C301" t="n">
+        <v>29</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>standard-universe-v1</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">
